--- a/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
+++ b/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GC-FID round1 raw" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GC-FID round1 raw" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -457,8 +457,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
-      </c>
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -486,7 +490,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1000</v>
+        <v>962</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -501,8 +505,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
-      </c>
+        <v>962</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -530,7 +538,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -545,8 +553,12 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
-      </c>
+        <v>982</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -574,11 +586,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1840</v>
+        <v>462.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -589,8 +601,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1840</v>
-      </c>
+        <v>462.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -618,11 +634,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1850</v>
+        <v>433.4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -633,8 +649,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1850</v>
-      </c>
+        <v>433.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -662,11 +682,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1860</v>
+        <v>502.4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -677,8 +697,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1860</v>
-      </c>
+        <v>502.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -706,7 +730,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>470</v>
+        <v>1487.3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -721,8 +745,12 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>470</v>
-      </c>
+        <v>1487.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -750,11 +778,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>480</v>
+        <v>1507</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
     </row>
@@ -765,8 +793,12 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>480</v>
-      </c>
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -794,11 +826,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>490</v>
+        <v>1536.6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
     </row>
@@ -809,8 +841,12 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>490</v>
-      </c>
+        <v>1536.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -838,11 +874,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2320</v>
+        <v>866.8</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
@@ -853,8 +889,12 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2320</v>
-      </c>
+        <v>866.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -882,11 +922,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2330</v>
+        <v>896.4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
@@ -897,8 +937,12 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2330</v>
-      </c>
+        <v>896.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -926,11 +970,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2340</v>
+        <v>847.1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
@@ -941,8 +985,12 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2340</v>
-      </c>
+        <v>847.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -970,11 +1018,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1540</v>
+        <v>1034.2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -985,8 +1033,12 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1540</v>
-      </c>
+        <v>1034.2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1014,11 +1066,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1550</v>
+        <v>1004.7</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1029,8 +1081,12 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1550</v>
-      </c>
+        <v>1004.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1058,11 +1114,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1560</v>
+        <v>1073.7</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -1073,8 +1129,12 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1560</v>
-      </c>
+        <v>1073.7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1102,11 +1162,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1190</v>
+        <v>1812.4</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -1117,8 +1177,12 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1190</v>
-      </c>
+        <v>1812.4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1146,11 +1210,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1200</v>
+        <v>1842</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -1161,8 +1225,12 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1200</v>
-      </c>
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1190,11 +1258,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1210</v>
+        <v>1832.1</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>E1</t>
         </is>
       </c>
     </row>
@@ -1205,8 +1273,12 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1210</v>
-      </c>
+        <v>1832.1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1234,11 +1306,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3100</v>
+        <v>1605.5</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>F1</t>
         </is>
       </c>
     </row>
@@ -1249,8 +1321,12 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3100</v>
-      </c>
+        <v>1605.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1278,11 +1354,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3110</v>
+        <v>1576</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>F1</t>
         </is>
       </c>
     </row>
@@ -1293,8 +1369,12 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3110</v>
-      </c>
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1322,11 +1402,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>3120</v>
+        <v>1635.1</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>F1</t>
         </is>
       </c>
     </row>
@@ -1337,8 +1417,588 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3120</v>
-      </c>
+        <v>1635.1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3063.3</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3063.3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3023.9</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3023.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>3083</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2255.7</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2255.7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2275.3</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2275.3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2295.1</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2295.1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1319.9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1290.4</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1290.4</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1349.5</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1349.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1162.3</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1162.3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1191.8</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1191.8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
+++ b/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
@@ -586,7 +586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>462.9</v>
+        <v>2373.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>462.9</v>
+        <v>2373.9</v>
       </c>
     </row>
     <row r="20">
@@ -634,7 +634,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>433.4</v>
+        <v>2344.3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>433.4</v>
+        <v>2344.3</v>
       </c>
     </row>
     <row r="25">
@@ -682,7 +682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>502.4</v>
+        <v>2403.4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>502.4</v>
+        <v>2403.4</v>
       </c>
     </row>
     <row r="30">
@@ -730,7 +730,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1487.3</v>
+        <v>1832.1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1487.3</v>
+        <v>1832.1</v>
       </c>
     </row>
     <row r="35">
@@ -778,7 +778,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1507</v>
+        <v>1802.6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1507</v>
+        <v>1802.6</v>
       </c>
     </row>
     <row r="40">
@@ -826,7 +826,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1536.6</v>
+        <v>1871.5</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1536.6</v>
+        <v>1871.5</v>
       </c>
     </row>
     <row r="45">
@@ -874,7 +874,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>866.8</v>
+        <v>3073.2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>866.8</v>
+        <v>3073.2</v>
       </c>
     </row>
     <row r="50">
@@ -922,7 +922,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>896.4</v>
+        <v>3023.9</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>896.4</v>
+        <v>3023.9</v>
       </c>
     </row>
     <row r="55">
@@ -970,7 +970,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>847.1</v>
+        <v>3102.8</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>847.1</v>
+        <v>3102.8</v>
       </c>
     </row>
     <row r="60">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1034.2</v>
+        <v>610.7</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1034.2</v>
+        <v>610.7</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1004.7</v>
+        <v>581.1</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1004.7</v>
+        <v>581.1</v>
       </c>
     </row>
     <row r="70">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1073.7</v>
+        <v>650.1</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1073.7</v>
+        <v>650.1</v>
       </c>
     </row>
     <row r="75">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1812.4</v>
+        <v>1516.9</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1812.4</v>
+        <v>1516.9</v>
       </c>
     </row>
     <row r="80">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1842</v>
+        <v>1487.3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1842</v>
+        <v>1487.3</v>
       </c>
     </row>
     <row r="85">
@@ -1258,7 +1258,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1832.1</v>
+        <v>1546.5</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1832.1</v>
+        <v>1546.5</v>
       </c>
     </row>
     <row r="90">
@@ -1306,7 +1306,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1605.5</v>
+        <v>1172.1</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1605.5</v>
+        <v>1172.1</v>
       </c>
     </row>
     <row r="95">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1576</v>
+        <v>1142.6</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1576</v>
+        <v>1142.6</v>
       </c>
     </row>
     <row r="100">
@@ -1402,7 +1402,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1635.1</v>
+        <v>1201.7</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1635.1</v>
+        <v>1201.7</v>
       </c>
     </row>
     <row r="105">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>3063.3</v>
+        <v>866.8</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3063.3</v>
+        <v>866.8</v>
       </c>
     </row>
     <row r="110">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3023.9</v>
+        <v>837.2</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3023.9</v>
+        <v>837.2</v>
       </c>
     </row>
     <row r="115">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3083</v>
+        <v>896.4</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3083</v>
+        <v>896.4</v>
       </c>
     </row>
     <row r="120">
@@ -1594,7 +1594,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2255.7</v>
+        <v>1310.1</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2255.7</v>
+        <v>1310.1</v>
       </c>
     </row>
     <row r="125">
@@ -1642,7 +1642,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2275.3</v>
+        <v>1280.5</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2275.3</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="130">
@@ -1690,7 +1690,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2295.1</v>
+        <v>1339.6</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2295.1</v>
+        <v>1339.6</v>
       </c>
     </row>
     <row r="135">
@@ -1738,7 +1738,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1319.9</v>
+        <v>462.9</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1319.9</v>
+        <v>462.9</v>
       </c>
     </row>
     <row r="140">
@@ -1786,7 +1786,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1290.4</v>
+        <v>433.4</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1290.4</v>
+        <v>433.4</v>
       </c>
     </row>
     <row r="145">
@@ -1834,7 +1834,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1349.5</v>
+        <v>492.5</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1349.5</v>
+        <v>492.5</v>
       </c>
     </row>
     <row r="150">
@@ -1882,7 +1882,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1182</v>
+        <v>1034.2</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1182</v>
+        <v>1034.2</v>
       </c>
     </row>
     <row r="155">
@@ -1930,7 +1930,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1162.3</v>
+        <v>1004.7</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1162.3</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="160">
@@ -1978,7 +1978,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1191.8</v>
+        <v>1063.8</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1191.8</v>
+        <v>1063.8</v>
       </c>
     </row>
     <row r="165">

--- a/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
+++ b/src-tauri/samples/mame/11_mame_gc_fid_round1_raw.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2000,6 +2000,870 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1398.7</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1398.7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>1359.3</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1359.3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1438.1</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1438.1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>699.3</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>669.8</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>669.8</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>728.9</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>728.9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>935.8</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>935.8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>906.2</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>906.2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>965.3</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1654.8</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1654.8</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1615.4</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1615.4</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1694.2</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1694.2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>541.8</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>541.8</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>512.2</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>512.2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>571.3</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>571.3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1142.6</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1142.6</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>1221.4</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1221.4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
